--- a/5.test_results/不備管理台帳_FY2025.xlsx
+++ b/5.test_results/不備管理台帳_FY2025.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -108,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,7 +123,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -134,6 +133,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,6 +529,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +590,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>退職者5名中2名のSAPアカウント停止が規程の3営業日を大きく超過(11日/18日)</t>
+          <t>退職者5名中2名のSAPアカウント停止が規程の3営業日を大きく超過(13日/18日)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -610,7 +613,7 @@
           <t>岡田 宏（情シス部長）/ 近藤 文子（人事部長）</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="11" t="n">
         <v>46112</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -655,7 +658,7 @@
           <t>木村 浩二（購買部長）/ 岡田 宏（情シス部長）</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="11" t="n">
         <v>46112</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -700,7 +703,7 @@
           <t>橋本 明（倉庫課長）/ 佐藤 一郎（経理部長）</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="11" t="n">
         <v>46112</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
